--- a/导航编辑.xlsx
+++ b/导航编辑.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work_space\open_code\my_nav_site\my-nav-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7A39EF-81C4-45F5-A711-B761E680ED67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87395C2C-7E14-4AC5-9A91-650CD9694354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{74864995-F056-45EB-86D8-F46758C8A787}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>分类</t>
   </si>
@@ -196,6 +196,14 @@
   </si>
   <si>
     <t>http://117.72.244.30:3001/</t>
+  </si>
+  <si>
+    <t>https://gtype.cc.cd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obsidian_sync</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -666,9 +674,14 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -873,6 +886,7 @@
   <hyperlinks>
     <hyperlink ref="C12" r:id="rId1" xr:uid="{EF24A0F8-8C11-4EDE-BB45-DA948123C97A}"/>
     <hyperlink ref="C11" r:id="rId2" xr:uid="{08AA0DD4-0CB8-45D0-B12F-ABCDE1D73D53}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{B4A18A2B-D72E-4DEF-8D92-7CCC45EB241A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
